--- a/templates/rider-template.xlsx
+++ b/templates/rider-template.xlsx
@@ -167,7 +167,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -184,7 +184,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -279,9 +287,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>531720</xdr:colOff>
+      <xdr:colOff>531360</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>329400</xdr:rowOff>
+      <xdr:rowOff>329040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -295,7 +303,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="66960" y="36000"/>
-          <a:ext cx="464760" cy="293400"/>
+          <a:ext cx="464400" cy="293040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -329,7 +337,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="9" style="1" width="11.57"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="33.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" s="4" customFormat="true" ht="33.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -343,361 +351,361 @@
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" customFormat="false" ht="35.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+    <row r="2" s="4" customFormat="true" ht="35.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5"/>
-      <c r="AG2" s="5"/>
-      <c r="AH2" s="5"/>
-      <c r="AI2" s="5"/>
-      <c r="AJ2" s="5"/>
-      <c r="AK2" s="5"/>
-      <c r="AL2" s="5"/>
-      <c r="AM2" s="5"/>
-      <c r="AN2" s="5"/>
-      <c r="AO2" s="5"/>
-      <c r="AP2" s="5"/>
-      <c r="AQ2" s="5"/>
-      <c r="AR2" s="5"/>
-      <c r="AS2" s="5"/>
-      <c r="AT2" s="5"/>
-      <c r="AU2" s="5"/>
-      <c r="AV2" s="5"/>
-      <c r="AW2" s="5"/>
-      <c r="AX2" s="5"/>
-      <c r="AY2" s="5"/>
-      <c r="AZ2" s="5"/>
-      <c r="BA2" s="5"/>
-      <c r="BB2" s="5"/>
-      <c r="BC2" s="5"/>
-      <c r="BD2" s="5"/>
-      <c r="BE2" s="5"/>
-      <c r="BF2" s="5"/>
-      <c r="BG2" s="5"/>
-      <c r="BH2" s="5"/>
-      <c r="BI2" s="5"/>
-      <c r="BJ2" s="5"/>
-      <c r="BK2" s="5"/>
-      <c r="BL2" s="5"/>
-      <c r="BM2" s="5"/>
-      <c r="BN2" s="5"/>
-      <c r="BO2" s="5"/>
-      <c r="BP2" s="5"/>
-      <c r="BQ2" s="5"/>
-      <c r="BR2" s="5"/>
-      <c r="BS2" s="5"/>
-      <c r="BT2" s="5"/>
-      <c r="BU2" s="5"/>
-      <c r="BV2" s="5"/>
-      <c r="BW2" s="5"/>
-      <c r="BX2" s="5"/>
-      <c r="BY2" s="5"/>
-      <c r="BZ2" s="5"/>
-      <c r="CA2" s="5"/>
-      <c r="CB2" s="5"/>
-      <c r="CC2" s="5"/>
-      <c r="CD2" s="5"/>
-      <c r="CE2" s="5"/>
-      <c r="CF2" s="5"/>
-      <c r="CG2" s="5"/>
-      <c r="CH2" s="5"/>
-      <c r="CI2" s="5"/>
-      <c r="CJ2" s="5"/>
-      <c r="CK2" s="5"/>
-      <c r="CL2" s="5"/>
-      <c r="CM2" s="5"/>
-      <c r="CN2" s="5"/>
-      <c r="CO2" s="5"/>
-      <c r="CP2" s="5"/>
-      <c r="CQ2" s="5"/>
-      <c r="CR2" s="5"/>
-      <c r="CS2" s="5"/>
-      <c r="CT2" s="5"/>
-      <c r="CU2" s="5"/>
-      <c r="CV2" s="5"/>
-      <c r="CW2" s="5"/>
-      <c r="CX2" s="5"/>
-      <c r="CY2" s="5"/>
-      <c r="CZ2" s="5"/>
-      <c r="DA2" s="5"/>
-      <c r="DB2" s="5"/>
-      <c r="DC2" s="5"/>
-      <c r="DD2" s="5"/>
-      <c r="DE2" s="5"/>
-      <c r="DF2" s="5"/>
-      <c r="DG2" s="5"/>
-      <c r="DH2" s="5"/>
-      <c r="DI2" s="5"/>
-      <c r="DJ2" s="5"/>
-      <c r="DK2" s="5"/>
-      <c r="DL2" s="5"/>
-      <c r="DM2" s="5"/>
-      <c r="DN2" s="5"/>
-      <c r="DO2" s="5"/>
-      <c r="DP2" s="5"/>
-      <c r="DQ2" s="5"/>
-      <c r="DR2" s="5"/>
-      <c r="DS2" s="5"/>
-      <c r="DT2" s="5"/>
-      <c r="DU2" s="5"/>
-      <c r="DV2" s="5"/>
-      <c r="DW2" s="5"/>
-      <c r="DX2" s="5"/>
-      <c r="DY2" s="5"/>
-      <c r="DZ2" s="5"/>
-      <c r="EA2" s="5"/>
-      <c r="EB2" s="5"/>
-      <c r="EC2" s="5"/>
-      <c r="ED2" s="5"/>
-      <c r="EE2" s="5"/>
-      <c r="EF2" s="5"/>
-      <c r="EG2" s="5"/>
-      <c r="EH2" s="5"/>
-      <c r="EI2" s="5"/>
-      <c r="EJ2" s="5"/>
-      <c r="EK2" s="5"/>
-      <c r="EL2" s="5"/>
-      <c r="EM2" s="5"/>
-      <c r="EN2" s="5"/>
-      <c r="EO2" s="5"/>
-      <c r="EP2" s="5"/>
-      <c r="EQ2" s="5"/>
-      <c r="ER2" s="5"/>
-      <c r="ES2" s="5"/>
-      <c r="ET2" s="5"/>
-      <c r="EU2" s="5"/>
-      <c r="EV2" s="5"/>
-      <c r="EW2" s="5"/>
-      <c r="EX2" s="5"/>
-      <c r="EY2" s="5"/>
-      <c r="EZ2" s="5"/>
-      <c r="FA2" s="5"/>
-      <c r="FB2" s="5"/>
-      <c r="FC2" s="5"/>
-      <c r="FD2" s="5"/>
-      <c r="FE2" s="5"/>
-      <c r="FF2" s="5"/>
-      <c r="FG2" s="5"/>
-      <c r="FH2" s="5"/>
-      <c r="FI2" s="5"/>
-      <c r="FJ2" s="5"/>
-      <c r="FK2" s="5"/>
-      <c r="FL2" s="5"/>
-      <c r="FM2" s="5"/>
-      <c r="FN2" s="5"/>
-      <c r="FO2" s="5"/>
-      <c r="FP2" s="5"/>
-      <c r="FQ2" s="5"/>
-      <c r="FR2" s="5"/>
-      <c r="FS2" s="5"/>
-      <c r="FT2" s="5"/>
-      <c r="FU2" s="5"/>
-      <c r="FV2" s="5"/>
-      <c r="FW2" s="5"/>
-      <c r="FX2" s="5"/>
-      <c r="FY2" s="5"/>
-      <c r="FZ2" s="5"/>
-      <c r="GA2" s="5"/>
-      <c r="GB2" s="5"/>
-      <c r="GC2" s="5"/>
-      <c r="GD2" s="5"/>
-      <c r="GE2" s="5"/>
-      <c r="GF2" s="5"/>
-      <c r="GG2" s="5"/>
-      <c r="GH2" s="5"/>
-      <c r="GI2" s="5"/>
-      <c r="GJ2" s="5"/>
-      <c r="GK2" s="5"/>
-      <c r="GL2" s="5"/>
-      <c r="GM2" s="5"/>
-      <c r="GN2" s="5"/>
-      <c r="GO2" s="5"/>
-      <c r="GP2" s="5"/>
-      <c r="GQ2" s="5"/>
-      <c r="GR2" s="5"/>
-      <c r="GS2" s="5"/>
-      <c r="GT2" s="5"/>
-      <c r="GU2" s="5"/>
-      <c r="GV2" s="5"/>
-      <c r="GW2" s="5"/>
-      <c r="GX2" s="5"/>
-      <c r="GY2" s="5"/>
-      <c r="GZ2" s="5"/>
-      <c r="HA2" s="5"/>
-      <c r="HB2" s="5"/>
-      <c r="HC2" s="5"/>
-      <c r="HD2" s="5"/>
-      <c r="HE2" s="5"/>
-      <c r="HF2" s="5"/>
-      <c r="HG2" s="5"/>
-      <c r="HH2" s="5"/>
-      <c r="HI2" s="5"/>
-      <c r="HJ2" s="5"/>
-      <c r="HK2" s="5"/>
-      <c r="HL2" s="5"/>
-      <c r="HM2" s="5"/>
-      <c r="HN2" s="5"/>
-      <c r="HO2" s="5"/>
-      <c r="HP2" s="5"/>
-      <c r="HQ2" s="5"/>
-      <c r="HR2" s="5"/>
-      <c r="HS2" s="5"/>
-      <c r="HT2" s="5"/>
-      <c r="HU2" s="5"/>
-      <c r="HV2" s="5"/>
-      <c r="HW2" s="5"/>
-      <c r="HX2" s="5"/>
-      <c r="HY2" s="5"/>
-      <c r="HZ2" s="5"/>
-      <c r="IA2" s="5"/>
-      <c r="IB2" s="5"/>
-      <c r="IC2" s="5"/>
-      <c r="ID2" s="5"/>
-      <c r="IE2" s="5"/>
-      <c r="IF2" s="5"/>
-      <c r="IG2" s="5"/>
-      <c r="IH2" s="5"/>
-      <c r="II2" s="5"/>
-      <c r="IJ2" s="5"/>
-      <c r="IK2" s="5"/>
-      <c r="IL2" s="5"/>
-      <c r="IM2" s="5"/>
-      <c r="IN2" s="5"/>
-      <c r="IO2" s="5"/>
-      <c r="IP2" s="5"/>
-      <c r="IQ2" s="5"/>
-      <c r="IR2" s="5"/>
-      <c r="IS2" s="5"/>
-      <c r="IT2" s="5"/>
-      <c r="IU2" s="5"/>
-      <c r="IV2" s="5"/>
-      <c r="IW2" s="5"/>
-      <c r="IX2" s="5"/>
-      <c r="IY2" s="5"/>
-      <c r="IZ2" s="5"/>
-      <c r="JA2" s="5"/>
-      <c r="JB2" s="5"/>
-      <c r="JC2" s="5"/>
-      <c r="JD2" s="5"/>
-      <c r="JE2" s="5"/>
-      <c r="JF2" s="5"/>
-      <c r="JG2" s="5"/>
-      <c r="JH2" s="5"/>
-      <c r="JI2" s="5"/>
-      <c r="JJ2" s="5"/>
-      <c r="JK2" s="5"/>
-      <c r="JL2" s="5"/>
-      <c r="JM2" s="5"/>
-      <c r="JN2" s="5"/>
-      <c r="JO2" s="5"/>
-      <c r="JP2" s="5"/>
-      <c r="JQ2" s="5"/>
-      <c r="JR2" s="5"/>
-      <c r="JS2" s="5"/>
-      <c r="JT2" s="5"/>
-      <c r="JU2" s="5"/>
-      <c r="JV2" s="5"/>
-      <c r="JW2" s="5"/>
-      <c r="JX2" s="5"/>
-      <c r="JY2" s="5"/>
-      <c r="JZ2" s="5"/>
-      <c r="KA2" s="5"/>
-      <c r="KB2" s="5"/>
-      <c r="KC2" s="5"/>
-      <c r="KD2" s="5"/>
-      <c r="KE2" s="5"/>
-      <c r="KF2" s="5"/>
-      <c r="KG2" s="5"/>
-      <c r="KH2" s="5"/>
-      <c r="KI2" s="5"/>
-      <c r="KJ2" s="5"/>
-      <c r="KK2" s="5"/>
-      <c r="KL2" s="5"/>
-      <c r="KM2" s="5"/>
-      <c r="KN2" s="5"/>
-      <c r="KO2" s="5"/>
-      <c r="KP2" s="5"/>
-      <c r="KQ2" s="5"/>
-      <c r="KR2" s="5"/>
-      <c r="KS2" s="5"/>
-      <c r="KT2" s="5"/>
-      <c r="KU2" s="5"/>
-      <c r="KV2" s="5"/>
-      <c r="KW2" s="5"/>
-      <c r="KX2" s="5"/>
-      <c r="KY2" s="5"/>
-      <c r="KZ2" s="5"/>
-      <c r="LA2" s="5"/>
-      <c r="LB2" s="5"/>
-      <c r="LC2" s="5"/>
-      <c r="LD2" s="5"/>
-      <c r="LE2" s="5"/>
-      <c r="LF2" s="5"/>
-      <c r="LG2" s="5"/>
-      <c r="LH2" s="5"/>
-      <c r="LI2" s="5"/>
-      <c r="LJ2" s="5"/>
-      <c r="LK2" s="5"/>
-      <c r="LL2" s="5"/>
-      <c r="LM2" s="5"/>
-      <c r="LN2" s="5"/>
-      <c r="LO2" s="5"/>
-      <c r="LP2" s="5"/>
-      <c r="LQ2" s="5"/>
-      <c r="LR2" s="5"/>
-      <c r="LS2" s="5"/>
-      <c r="LT2" s="5"/>
-      <c r="LU2" s="5"/>
-      <c r="LV2" s="5"/>
-      <c r="LW2" s="5"/>
-      <c r="LX2" s="5"/>
-      <c r="LY2" s="5"/>
-      <c r="AMJ2" s="4"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6"/>
+      <c r="AK2" s="6"/>
+      <c r="AL2" s="6"/>
+      <c r="AM2" s="6"/>
+      <c r="AN2" s="6"/>
+      <c r="AO2" s="6"/>
+      <c r="AP2" s="6"/>
+      <c r="AQ2" s="6"/>
+      <c r="AR2" s="6"/>
+      <c r="AS2" s="6"/>
+      <c r="AT2" s="6"/>
+      <c r="AU2" s="6"/>
+      <c r="AV2" s="6"/>
+      <c r="AW2" s="6"/>
+      <c r="AX2" s="6"/>
+      <c r="AY2" s="6"/>
+      <c r="AZ2" s="6"/>
+      <c r="BA2" s="6"/>
+      <c r="BB2" s="6"/>
+      <c r="BC2" s="6"/>
+      <c r="BD2" s="6"/>
+      <c r="BE2" s="6"/>
+      <c r="BF2" s="6"/>
+      <c r="BG2" s="6"/>
+      <c r="BH2" s="6"/>
+      <c r="BI2" s="6"/>
+      <c r="BJ2" s="6"/>
+      <c r="BK2" s="6"/>
+      <c r="BL2" s="6"/>
+      <c r="BM2" s="6"/>
+      <c r="BN2" s="6"/>
+      <c r="BO2" s="6"/>
+      <c r="BP2" s="6"/>
+      <c r="BQ2" s="6"/>
+      <c r="BR2" s="6"/>
+      <c r="BS2" s="6"/>
+      <c r="BT2" s="6"/>
+      <c r="BU2" s="6"/>
+      <c r="BV2" s="6"/>
+      <c r="BW2" s="6"/>
+      <c r="BX2" s="6"/>
+      <c r="BY2" s="6"/>
+      <c r="BZ2" s="6"/>
+      <c r="CA2" s="6"/>
+      <c r="CB2" s="6"/>
+      <c r="CC2" s="6"/>
+      <c r="CD2" s="6"/>
+      <c r="CE2" s="6"/>
+      <c r="CF2" s="6"/>
+      <c r="CG2" s="6"/>
+      <c r="CH2" s="6"/>
+      <c r="CI2" s="6"/>
+      <c r="CJ2" s="6"/>
+      <c r="CK2" s="6"/>
+      <c r="CL2" s="6"/>
+      <c r="CM2" s="6"/>
+      <c r="CN2" s="6"/>
+      <c r="CO2" s="6"/>
+      <c r="CP2" s="6"/>
+      <c r="CQ2" s="6"/>
+      <c r="CR2" s="6"/>
+      <c r="CS2" s="6"/>
+      <c r="CT2" s="6"/>
+      <c r="CU2" s="6"/>
+      <c r="CV2" s="6"/>
+      <c r="CW2" s="6"/>
+      <c r="CX2" s="6"/>
+      <c r="CY2" s="6"/>
+      <c r="CZ2" s="6"/>
+      <c r="DA2" s="6"/>
+      <c r="DB2" s="6"/>
+      <c r="DC2" s="6"/>
+      <c r="DD2" s="6"/>
+      <c r="DE2" s="6"/>
+      <c r="DF2" s="6"/>
+      <c r="DG2" s="6"/>
+      <c r="DH2" s="6"/>
+      <c r="DI2" s="6"/>
+      <c r="DJ2" s="6"/>
+      <c r="DK2" s="6"/>
+      <c r="DL2" s="6"/>
+      <c r="DM2" s="6"/>
+      <c r="DN2" s="6"/>
+      <c r="DO2" s="6"/>
+      <c r="DP2" s="6"/>
+      <c r="DQ2" s="6"/>
+      <c r="DR2" s="6"/>
+      <c r="DS2" s="6"/>
+      <c r="DT2" s="6"/>
+      <c r="DU2" s="6"/>
+      <c r="DV2" s="6"/>
+      <c r="DW2" s="6"/>
+      <c r="DX2" s="6"/>
+      <c r="DY2" s="6"/>
+      <c r="DZ2" s="6"/>
+      <c r="EA2" s="6"/>
+      <c r="EB2" s="6"/>
+      <c r="EC2" s="6"/>
+      <c r="ED2" s="6"/>
+      <c r="EE2" s="6"/>
+      <c r="EF2" s="6"/>
+      <c r="EG2" s="6"/>
+      <c r="EH2" s="6"/>
+      <c r="EI2" s="6"/>
+      <c r="EJ2" s="6"/>
+      <c r="EK2" s="6"/>
+      <c r="EL2" s="6"/>
+      <c r="EM2" s="6"/>
+      <c r="EN2" s="6"/>
+      <c r="EO2" s="6"/>
+      <c r="EP2" s="6"/>
+      <c r="EQ2" s="6"/>
+      <c r="ER2" s="6"/>
+      <c r="ES2" s="6"/>
+      <c r="ET2" s="6"/>
+      <c r="EU2" s="6"/>
+      <c r="EV2" s="6"/>
+      <c r="EW2" s="6"/>
+      <c r="EX2" s="6"/>
+      <c r="EY2" s="6"/>
+      <c r="EZ2" s="6"/>
+      <c r="FA2" s="6"/>
+      <c r="FB2" s="6"/>
+      <c r="FC2" s="6"/>
+      <c r="FD2" s="6"/>
+      <c r="FE2" s="6"/>
+      <c r="FF2" s="6"/>
+      <c r="FG2" s="6"/>
+      <c r="FH2" s="6"/>
+      <c r="FI2" s="6"/>
+      <c r="FJ2" s="6"/>
+      <c r="FK2" s="6"/>
+      <c r="FL2" s="6"/>
+      <c r="FM2" s="6"/>
+      <c r="FN2" s="6"/>
+      <c r="FO2" s="6"/>
+      <c r="FP2" s="6"/>
+      <c r="FQ2" s="6"/>
+      <c r="FR2" s="6"/>
+      <c r="FS2" s="6"/>
+      <c r="FT2" s="6"/>
+      <c r="FU2" s="6"/>
+      <c r="FV2" s="6"/>
+      <c r="FW2" s="6"/>
+      <c r="FX2" s="6"/>
+      <c r="FY2" s="6"/>
+      <c r="FZ2" s="6"/>
+      <c r="GA2" s="6"/>
+      <c r="GB2" s="6"/>
+      <c r="GC2" s="6"/>
+      <c r="GD2" s="6"/>
+      <c r="GE2" s="6"/>
+      <c r="GF2" s="6"/>
+      <c r="GG2" s="6"/>
+      <c r="GH2" s="6"/>
+      <c r="GI2" s="6"/>
+      <c r="GJ2" s="6"/>
+      <c r="GK2" s="6"/>
+      <c r="GL2" s="6"/>
+      <c r="GM2" s="6"/>
+      <c r="GN2" s="6"/>
+      <c r="GO2" s="6"/>
+      <c r="GP2" s="6"/>
+      <c r="GQ2" s="6"/>
+      <c r="GR2" s="6"/>
+      <c r="GS2" s="6"/>
+      <c r="GT2" s="6"/>
+      <c r="GU2" s="6"/>
+      <c r="GV2" s="6"/>
+      <c r="GW2" s="6"/>
+      <c r="GX2" s="6"/>
+      <c r="GY2" s="6"/>
+      <c r="GZ2" s="6"/>
+      <c r="HA2" s="6"/>
+      <c r="HB2" s="6"/>
+      <c r="HC2" s="6"/>
+      <c r="HD2" s="6"/>
+      <c r="HE2" s="6"/>
+      <c r="HF2" s="6"/>
+      <c r="HG2" s="6"/>
+      <c r="HH2" s="6"/>
+      <c r="HI2" s="6"/>
+      <c r="HJ2" s="6"/>
+      <c r="HK2" s="6"/>
+      <c r="HL2" s="6"/>
+      <c r="HM2" s="6"/>
+      <c r="HN2" s="6"/>
+      <c r="HO2" s="6"/>
+      <c r="HP2" s="6"/>
+      <c r="HQ2" s="6"/>
+      <c r="HR2" s="6"/>
+      <c r="HS2" s="6"/>
+      <c r="HT2" s="6"/>
+      <c r="HU2" s="6"/>
+      <c r="HV2" s="6"/>
+      <c r="HW2" s="6"/>
+      <c r="HX2" s="6"/>
+      <c r="HY2" s="6"/>
+      <c r="HZ2" s="6"/>
+      <c r="IA2" s="6"/>
+      <c r="IB2" s="6"/>
+      <c r="IC2" s="6"/>
+      <c r="ID2" s="6"/>
+      <c r="IE2" s="6"/>
+      <c r="IF2" s="6"/>
+      <c r="IG2" s="6"/>
+      <c r="IH2" s="6"/>
+      <c r="II2" s="6"/>
+      <c r="IJ2" s="6"/>
+      <c r="IK2" s="6"/>
+      <c r="IL2" s="6"/>
+      <c r="IM2" s="6"/>
+      <c r="IN2" s="6"/>
+      <c r="IO2" s="6"/>
+      <c r="IP2" s="6"/>
+      <c r="IQ2" s="6"/>
+      <c r="IR2" s="6"/>
+      <c r="IS2" s="6"/>
+      <c r="IT2" s="6"/>
+      <c r="IU2" s="6"/>
+      <c r="IV2" s="6"/>
+      <c r="IW2" s="6"/>
+      <c r="IX2" s="6"/>
+      <c r="IY2" s="6"/>
+      <c r="IZ2" s="6"/>
+      <c r="JA2" s="6"/>
+      <c r="JB2" s="6"/>
+      <c r="JC2" s="6"/>
+      <c r="JD2" s="6"/>
+      <c r="JE2" s="6"/>
+      <c r="JF2" s="6"/>
+      <c r="JG2" s="6"/>
+      <c r="JH2" s="6"/>
+      <c r="JI2" s="6"/>
+      <c r="JJ2" s="6"/>
+      <c r="JK2" s="6"/>
+      <c r="JL2" s="6"/>
+      <c r="JM2" s="6"/>
+      <c r="JN2" s="6"/>
+      <c r="JO2" s="6"/>
+      <c r="JP2" s="6"/>
+      <c r="JQ2" s="6"/>
+      <c r="JR2" s="6"/>
+      <c r="JS2" s="6"/>
+      <c r="JT2" s="6"/>
+      <c r="JU2" s="6"/>
+      <c r="JV2" s="6"/>
+      <c r="JW2" s="6"/>
+      <c r="JX2" s="6"/>
+      <c r="JY2" s="6"/>
+      <c r="JZ2" s="6"/>
+      <c r="KA2" s="6"/>
+      <c r="KB2" s="6"/>
+      <c r="KC2" s="6"/>
+      <c r="KD2" s="6"/>
+      <c r="KE2" s="6"/>
+      <c r="KF2" s="6"/>
+      <c r="KG2" s="6"/>
+      <c r="KH2" s="6"/>
+      <c r="KI2" s="6"/>
+      <c r="KJ2" s="6"/>
+      <c r="KK2" s="6"/>
+      <c r="KL2" s="6"/>
+      <c r="KM2" s="6"/>
+      <c r="KN2" s="6"/>
+      <c r="KO2" s="6"/>
+      <c r="KP2" s="6"/>
+      <c r="KQ2" s="6"/>
+      <c r="KR2" s="6"/>
+      <c r="KS2" s="6"/>
+      <c r="KT2" s="6"/>
+      <c r="KU2" s="6"/>
+      <c r="KV2" s="6"/>
+      <c r="KW2" s="6"/>
+      <c r="KX2" s="6"/>
+      <c r="KY2" s="6"/>
+      <c r="KZ2" s="6"/>
+      <c r="LA2" s="6"/>
+      <c r="LB2" s="6"/>
+      <c r="LC2" s="6"/>
+      <c r="LD2" s="6"/>
+      <c r="LE2" s="6"/>
+      <c r="LF2" s="6"/>
+      <c r="LG2" s="6"/>
+      <c r="LH2" s="6"/>
+      <c r="LI2" s="6"/>
+      <c r="LJ2" s="6"/>
+      <c r="LK2" s="6"/>
+      <c r="LL2" s="6"/>
+      <c r="LM2" s="6"/>
+      <c r="LN2" s="6"/>
+      <c r="LO2" s="6"/>
+      <c r="LP2" s="6"/>
+      <c r="LQ2" s="6"/>
+      <c r="LR2" s="6"/>
+      <c r="LS2" s="6"/>
+      <c r="LT2" s="6"/>
+      <c r="LU2" s="6"/>
+      <c r="LV2" s="6"/>
+      <c r="LW2" s="6"/>
+      <c r="LX2" s="6"/>
+      <c r="LY2" s="6"/>
+      <c r="AMJ2" s="5"/>
     </row>
-    <row r="3" s="5" customFormat="true" ht="34.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="7" customFormat="true" ht="34.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1038,7 +1046,7 @@
       <c r="AMJ3" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="34.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F6" s="6"/>
+      <c r="F6" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
